--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -36,69 +36,69 @@
     <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
+    <t xml:space="preserve">Ñiquén</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Nicolás</t>
   </si>
   <si>
+    <t xml:space="preserve">Chillán Viejo</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pinto</t>
   </si>
   <si>
+    <t xml:space="preserve">Coelemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cobquecura</t>
+  </si>
+  <si>
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
+    <t xml:space="preserve">Ranquil</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Carmen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quirihue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Portezuelo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yungay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bulnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treguaco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coihueco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ninhue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pemuco</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Carlos</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Fabián</t>
   </si>
   <si>
-    <t xml:space="preserve">Portezuelo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cobquecura</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coelemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yungay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coihueco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bulnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ninhue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Carmen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quirihue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Chillán Viejo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Carlos</t>
+    <t xml:space="preserve">San Ignacio</t>
   </si>
   <si>
     <t xml:space="preserve">Chillán</t>
   </si>
   <si>
-    <t xml:space="preserve">San Ignacio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pemuco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ranquil</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treguaco</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ñiquén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -538,13 +538,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>16305</v>
+        <v>16303</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>9.6</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="3">
@@ -555,13 +555,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>16106</v>
+        <v>16305</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>8.96</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="4">
@@ -572,13 +572,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>16107</v>
+        <v>16103</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>7.21</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="5">
@@ -589,13 +589,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>16304</v>
+        <v>16106</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.8</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="6">
@@ -606,13 +606,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>16205</v>
+        <v>16203</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.29</v>
+        <v>4.59</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.02</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="8">
@@ -640,13 +640,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>16203</v>
+        <v>16107</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1.95</v>
+        <v>3.68</v>
       </c>
     </row>
     <row r="9">
@@ -657,13 +657,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>16109</v>
+        <v>16206</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1.74</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="10">
@@ -674,13 +674,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>16302</v>
+        <v>16104</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1.19</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="11">
@@ -691,13 +691,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>16102</v>
+        <v>16201</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1.11</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="12">
@@ -708,13 +708,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>16204</v>
+        <v>16205</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>0.94</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="13">
@@ -725,13 +725,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>16104</v>
+        <v>16109</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.74</v>
+        <v>3.05</v>
       </c>
     </row>
     <row r="14">
@@ -742,13 +742,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>16201</v>
+        <v>16102</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>0.53</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="15">
@@ -759,13 +759,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>16103</v>
+        <v>16207</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>0.45</v>
+        <v>2.91</v>
       </c>
     </row>
     <row r="16">
@@ -776,13 +776,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>16301</v>
+        <v>16302</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.32</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="17">
@@ -793,13 +793,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>16101</v>
+        <v>16204</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>-0.98</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="18">
@@ -810,13 +810,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>16108</v>
+        <v>16105</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>-2.35</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="19">
@@ -827,13 +827,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>16105</v>
+        <v>16301</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>-5.27</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="20">
@@ -844,13 +844,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>16206</v>
+        <v>16304</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-5.73</v>
+        <v>1.29</v>
       </c>
     </row>
     <row r="21">
@@ -861,13 +861,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>16207</v>
+        <v>16108</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-5.93</v>
+        <v>0.74</v>
       </c>
     </row>
     <row r="22">
@@ -878,13 +878,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>16303</v>
+        <v>16101</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>-22.08</v>
+        <v>0.07</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -544,7 +544,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>11.19</v>
+        <v>111.94</v>
       </c>
     </row>
     <row r="3">
@@ -561,7 +561,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>9.32</v>
+        <v>93.19</v>
       </c>
     </row>
     <row r="4">
@@ -578,7 +578,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>5.8</v>
+        <v>58.03</v>
       </c>
     </row>
     <row r="5">
@@ -595,7 +595,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>5.5</v>
+        <v>54.95</v>
       </c>
     </row>
     <row r="6">
@@ -612,7 +612,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.59</v>
+        <v>45.93</v>
       </c>
     </row>
     <row r="7">
@@ -629,7 +629,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.32</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="8">
@@ -646,7 +646,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.68</v>
+        <v>36.78</v>
       </c>
     </row>
     <row r="9">
@@ -663,7 +663,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.65</v>
+        <v>36.5</v>
       </c>
     </row>
     <row r="10">
@@ -680,7 +680,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>3.28</v>
+        <v>32.85</v>
       </c>
     </row>
     <row r="11">
@@ -697,7 +697,7 @@
         <v>2022</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>3.12</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="12">
@@ -714,7 +714,7 @@
         <v>2022</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>3.05</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="13">
@@ -731,7 +731,7 @@
         <v>2022</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>3.05</v>
+        <v>30.49</v>
       </c>
     </row>
     <row r="14">
@@ -748,7 +748,7 @@
         <v>2022</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>3.04</v>
+        <v>30.36</v>
       </c>
     </row>
     <row r="15">
@@ -765,7 +765,7 @@
         <v>2022</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>2.91</v>
+        <v>29.11</v>
       </c>
     </row>
     <row r="16">
@@ -782,7 +782,7 @@
         <v>2022</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>2.89</v>
+        <v>28.91</v>
       </c>
     </row>
     <row r="17">
@@ -799,7 +799,7 @@
         <v>2022</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>2.63</v>
+        <v>26.27</v>
       </c>
     </row>
     <row r="18">
@@ -816,7 +816,7 @@
         <v>2022</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>2.34</v>
+        <v>23.44</v>
       </c>
     </row>
     <row r="19">
@@ -833,7 +833,7 @@
         <v>2022</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.73</v>
+        <v>17.31</v>
       </c>
     </row>
     <row r="20">
@@ -850,7 +850,7 @@
         <v>2022</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.29</v>
+        <v>12.9</v>
       </c>
     </row>
     <row r="21">
@@ -867,7 +867,7 @@
         <v>2022</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.74</v>
+        <v>7.36</v>
       </c>
     </row>
     <row r="22">
@@ -884,7 +884,7 @@
         <v>2022</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.07</v>
+        <v>0.67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -57,7 +57,7 @@
     <t xml:space="preserve">Quillón</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">El Carmen</t>
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:34</t>
+    <t xml:space="preserve">2026-10-04 08:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2022_nuble.xlsx
@@ -108,7 +108,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:17</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
